--- a/data/trans_orig/P19C01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C01-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124454</t>
+          <t>124042</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163696</t>
+          <t>162956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93301</t>
+          <t>94845</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126382</t>
+          <t>127907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229478</t>
+          <t>229538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>279810</t>
+          <t>278023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224110</t>
+          <t>224850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263352</t>
+          <t>263764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141905</t>
+          <t>140380</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174986</t>
+          <t>173442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>376284</t>
+          <t>378071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>426616</t>
+          <t>426556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76712</t>
+          <t>74909</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112665</t>
+          <t>109676</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109113</t>
+          <t>107777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145161</t>
+          <t>145980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194084</t>
+          <t>195243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>243095</t>
+          <t>245958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>187540</t>
+          <t>190529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>223493</t>
+          <t>225296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188404</t>
+          <t>187585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>224452</t>
+          <t>225788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390675</t>
+          <t>387812</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>439686</t>
+          <t>438527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100026</t>
+          <t>99732</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136284</t>
+          <t>138337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38632</t>
+          <t>38580</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60312</t>
+          <t>61094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144748</t>
+          <t>145809</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188640</t>
+          <t>187452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293983</t>
+          <t>291930</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330241</t>
+          <t>330535</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79756</t>
+          <t>78974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101436</t>
+          <t>101488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>381695</t>
+          <t>382883</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>425587</t>
+          <t>424526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181324</t>
+          <t>186201</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234321</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>174699</t>
+          <t>176287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>222176</t>
+          <t>222982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378094</t>
+          <t>376336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>448459</t>
+          <t>444399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>637133</t>
+          <t>634544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>690130</t>
+          <t>685253</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>373142</t>
+          <t>372336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>420619</t>
+          <t>419031</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1018313</t>
+          <t>1022373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1088678</t>
+          <t>1090436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57383</t>
+          <t>56442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85235</t>
+          <t>85853</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110420</t>
+          <t>113443</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150321</t>
+          <t>150057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178985</t>
+          <t>177843</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226011</t>
+          <t>228309</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162692</t>
+          <t>162074</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190544</t>
+          <t>191485</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>305759</t>
+          <t>306023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>345660</t>
+          <t>342637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>477996</t>
+          <t>475698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>525022</t>
+          <t>526164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80145</t>
+          <t>79642</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109193</t>
+          <t>109745</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>218063</t>
+          <t>216491</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>271071</t>
+          <t>266589</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>307100</t>
+          <t>306145</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>365215</t>
+          <t>367938</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>103040</t>
+          <t>102488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>132088</t>
+          <t>132591</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>674545</t>
+          <t>679027</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>727553</t>
+          <t>729125</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>792634</t>
+          <t>789911</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>850749</t>
+          <t>851704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>683327</t>
+          <t>684726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>776182</t>
+          <t>776969</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>810669</t>
+          <t>811432</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>909471</t>
+          <t>910316</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1524012</t>
+          <t>1522879</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1653528</t>
+          <t>1655008</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1673710</t>
+          <t>1672923</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1766565</t>
+          <t>1765166</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1829462</t>
+          <t>1828617</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1928264</t>
+          <t>1927501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3535297</t>
+          <t>3533817</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3664813</t>
+          <t>3665946</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126750</t>
+          <t>124383</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166238</t>
+          <t>165526</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117782</t>
+          <t>117289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153584</t>
+          <t>151950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252049</t>
+          <t>252853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309426</t>
+          <t>306637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,49%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229106</t>
+          <t>229818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268594</t>
+          <t>270961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140370</t>
+          <t>142004</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176172</t>
+          <t>176665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>379873</t>
+          <t>382662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>437250</t>
+          <t>436446</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,32%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121282</t>
+          <t>121475</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161857</t>
+          <t>161963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125188</t>
+          <t>124641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>162654</t>
+          <t>160404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257988</t>
+          <t>255260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>314760</t>
+          <t>313819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>221867</t>
+          <t>221761</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262442</t>
+          <t>262249</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150847</t>
+          <t>153097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>188313</t>
+          <t>188860</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>382465</t>
+          <t>383406</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>439237</t>
+          <t>441965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121307</t>
+          <t>121870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164251</t>
+          <t>162525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64279</t>
+          <t>63962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94176</t>
+          <t>93028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193055</t>
+          <t>197369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>246761</t>
+          <t>247794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>371237</t>
+          <t>372963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>414181</t>
+          <t>413618</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146460</t>
+          <t>147608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>176674</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>529363</t>
+          <t>528330</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>583069</t>
+          <t>578755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>74,57%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205452</t>
+          <t>205319</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>261041</t>
+          <t>263389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>225929</t>
+          <t>222946</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275715</t>
+          <t>275125</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>441735</t>
+          <t>445556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>516681</t>
+          <t>518960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>711688</t>
+          <t>709340</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>767277</t>
+          <t>767410</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>422215</t>
+          <t>422805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472001</t>
+          <t>474984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1153977</t>
+          <t>1151698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1228923</t>
+          <t>1225102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70289</t>
+          <t>69920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102315</t>
+          <t>101817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152849</t>
+          <t>150316</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199608</t>
+          <t>197604</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231482</t>
+          <t>231837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>287697</t>
+          <t>288047</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>300997</t>
+          <t>301495</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333023</t>
+          <t>333392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>470215</t>
+          <t>472219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>516974</t>
+          <t>519507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>785438</t>
+          <t>785088</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>841653</t>
+          <t>841298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97131</t>
+          <t>97192</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>127417</t>
+          <t>126605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>270525</t>
+          <t>269655</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>328804</t>
+          <t>326023</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>380464</t>
+          <t>380695</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>441992</t>
+          <t>446472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93786</t>
+          <t>94598</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124072</t>
+          <t>124011</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>596581</t>
+          <t>599362</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>654860</t>
+          <t>655730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>704596</t>
+          <t>700116</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>766124</t>
+          <t>765893</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,8%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>805280</t>
+          <t>802590</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>907488</t>
+          <t>906116</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1019795</t>
+          <t>1025778</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1130861</t>
+          <t>1138141</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1854323</t>
+          <t>1857845</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2001747</t>
+          <t>2006713</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2004312</t>
+          <t>2005684</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2106520</t>
+          <t>2109210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2010369</t>
+          <t>2003089</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2121435</t>
+          <t>2115452</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4051283</t>
+          <t>4046317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4198707</t>
+          <t>4195185</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>176586</t>
+          <t>176436</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>218931</t>
+          <t>218797</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>150064</t>
+          <t>149439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185500</t>
+          <t>184917</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>338530</t>
+          <t>337592</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>393261</t>
+          <t>392556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168683</t>
+          <t>168817</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>211028</t>
+          <t>211178</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130316</t>
+          <t>130899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>165752</t>
+          <t>166377</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>310169</t>
+          <t>310874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>364900</t>
+          <t>365838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>127099</t>
+          <t>130210</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165539</t>
+          <t>165226</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162829</t>
+          <t>161432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>198300</t>
+          <t>198920</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>301403</t>
+          <t>302049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>354969</t>
+          <t>355949</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151119</t>
+          <t>151432</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189559</t>
+          <t>186448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135275</t>
+          <t>134655</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>170746</t>
+          <t>172143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295263</t>
+          <t>294283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>348829</t>
+          <t>348183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,55%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133688</t>
+          <t>133406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>172006</t>
+          <t>174397</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36486</t>
+          <t>36049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59291</t>
+          <t>57384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178987</t>
+          <t>176770</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225083</t>
+          <t>223566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233205</t>
+          <t>230814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271523</t>
+          <t>271805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80130</t>
+          <t>82037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102935</t>
+          <t>103372</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319550</t>
+          <t>321067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>365646</t>
+          <t>367863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>292836</t>
+          <t>294111</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>350361</t>
+          <t>353012</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>246565</t>
+          <t>244318</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>296950</t>
+          <t>297020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>554327</t>
+          <t>552036</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>632594</t>
+          <t>631362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>529144</t>
+          <t>526493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>586669</t>
+          <t>585394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>387081</t>
+          <t>387011</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>437466</t>
+          <t>439713</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>930942</t>
+          <t>932174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1009209</t>
+          <t>1011500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,69%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110255</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>148046</t>
+          <t>149166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>186766</t>
+          <t>188516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>232799</t>
+          <t>233672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305786</t>
+          <t>308879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366903</t>
+          <t>368662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>277123</t>
+          <t>276003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>314914</t>
+          <t>314738</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>324682</t>
+          <t>323809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>370715</t>
+          <t>368965</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>615747</t>
+          <t>613988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>676864</t>
+          <t>673771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,57%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>117306</t>
+          <t>117574</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147368</t>
+          <t>148151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>336819</t>
+          <t>337935</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>394831</t>
+          <t>394612</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>467049</t>
+          <t>466259</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>530833</t>
+          <t>531562</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94180</t>
+          <t>93397</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124242</t>
+          <t>123974</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>430458</t>
+          <t>430677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>488470</t>
+          <t>487354</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>536004</t>
+          <t>535275</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>599788</t>
+          <t>600578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,3%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1030310</t>
+          <t>1023991</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1127126</t>
+          <t>1131710</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1188552</t>
+          <t>1193032</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1299894</t>
+          <t>1296669</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2251771</t>
+          <t>2247329</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2393447</t>
+          <t>2396034</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1528579</t>
+          <t>1523995</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1625395</t>
+          <t>1631714</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1555719</t>
+          <t>1558944</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1667061</t>
+          <t>1662581</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3117871</t>
+          <t>3115284</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3259547</t>
+          <t>3263989</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2023 (tasa de respuesta: 99,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>316428</t>
+          <t>317417</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>360246</t>
+          <t>359018</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>278292</t>
+          <t>276292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>311340</t>
+          <t>310157</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>604258</t>
+          <t>604120</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>661038</t>
+          <t>658877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,09%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138940</t>
+          <t>140168</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>182758</t>
+          <t>181769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129585</t>
+          <t>130768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>162633</t>
+          <t>164633</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>279073</t>
+          <t>281234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>335853</t>
+          <t>335991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>274364</t>
+          <t>275568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>314019</t>
+          <t>316233</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240350</t>
+          <t>240091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>271512</t>
+          <t>272882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>522236</t>
+          <t>522701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>576787</t>
+          <t>573130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134399</t>
+          <t>132185</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174054</t>
+          <t>172850</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106094</t>
+          <t>104724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>137256</t>
+          <t>137515</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>249236</t>
+          <t>252893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>303787</t>
+          <t>303322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85442</t>
+          <t>93586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>381540</t>
+          <t>382921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81541</t>
+          <t>81315</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101691</t>
+          <t>102132</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147574</t>
+          <t>137756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>476109</t>
+          <t>474993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279189</t>
+          <t>277808</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>575287</t>
+          <t>567143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63277</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83427</t>
+          <t>83653</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>349588</t>
+          <t>350704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>678123</t>
+          <t>687941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>484708</t>
+          <t>481880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>552987</t>
+          <t>548228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253064</t>
+          <t>241065</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>588487</t>
+          <t>592223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>666896</t>
+          <t>719083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1103838</t>
+          <t>1103506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>445164</t>
+          <t>449923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>513443</t>
+          <t>516271</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370382</t>
+          <t>366646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>705805</t>
+          <t>717804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>853182</t>
+          <t>853514</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1290124</t>
+          <t>1237937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182041</t>
+          <t>183013</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227033</t>
+          <t>227579</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>371938</t>
+          <t>367758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>522568</t>
+          <t>509445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>569112</t>
+          <t>568037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>732858</t>
+          <t>729429</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,22%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>211819</t>
+          <t>211273</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>256811</t>
+          <t>255839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>291413</t>
+          <t>304536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442043</t>
+          <t>446223</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>519975</t>
+          <t>523404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>683721</t>
+          <t>684796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>123367</t>
+          <t>126462</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175857</t>
+          <t>177681</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>404153</t>
+          <t>401959</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>452435</t>
+          <t>455152</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>551405</t>
+          <t>544289</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>619676</t>
+          <t>619301</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,38%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57355</t>
+          <t>55531</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>109845</t>
+          <t>106750</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>291475</t>
+          <t>288758</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>339757</t>
+          <t>341951</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>357446</t>
+          <t>357821</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>425717</t>
+          <t>432833</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1336940</t>
+          <t>1333874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1903952</t>
+          <t>1898138</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1562609</t>
+          <t>1538777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2106462</t>
+          <t>2107687</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3215788</t>
+          <t>3193359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3961712</t>
+          <t>3968116</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,54%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1374596</t>
+          <t>1380410</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1941608</t>
+          <t>1944674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1393797</t>
+          <t>1392572</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1937650</t>
+          <t>1961482</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2817095</t>
+          <t>2810691</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3563019</t>
+          <t>3585448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,89%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C01-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124042</t>
+          <t>124938</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162956</t>
+          <t>164728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94845</t>
+          <t>94745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127907</t>
+          <t>126010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229538</t>
+          <t>228314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278023</t>
+          <t>278675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224850</t>
+          <t>223078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263764</t>
+          <t>262868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140380</t>
+          <t>142277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>173442</t>
+          <t>173542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378071</t>
+          <t>377419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>426556</t>
+          <t>427780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74909</t>
+          <t>77085</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109676</t>
+          <t>108866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107777</t>
+          <t>108244</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145980</t>
+          <t>147355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195243</t>
+          <t>194795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245958</t>
+          <t>247001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>190529</t>
+          <t>191339</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>225296</t>
+          <t>223120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>187585</t>
+          <t>186210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>225788</t>
+          <t>225321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>387812</t>
+          <t>386769</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>438527</t>
+          <t>438975</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99732</t>
+          <t>97422</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138337</t>
+          <t>136007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38580</t>
+          <t>37758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61094</t>
+          <t>60848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145809</t>
+          <t>145774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187452</t>
+          <t>188538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>291930</t>
+          <t>294260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330535</t>
+          <t>332845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78974</t>
+          <t>79220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101488</t>
+          <t>102310</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>382883</t>
+          <t>381797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>424526</t>
+          <t>424561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186201</t>
+          <t>188619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>242085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>176287</t>
+          <t>172856</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>222982</t>
+          <t>219655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>376336</t>
+          <t>378367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>444399</t>
+          <t>450535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>634544</t>
+          <t>629369</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>685253</t>
+          <t>682835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>372336</t>
+          <t>375663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>419031</t>
+          <t>422462</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1022373</t>
+          <t>1016237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1090436</t>
+          <t>1088405</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56442</t>
+          <t>56490</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85853</t>
+          <t>85408</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113443</t>
+          <t>112393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150057</t>
+          <t>151294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>177843</t>
+          <t>178220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228309</t>
+          <t>229238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162074</t>
+          <t>162519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191485</t>
+          <t>191437</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>306023</t>
+          <t>304786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>342637</t>
+          <t>343687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>475698</t>
+          <t>474769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>526164</t>
+          <t>525787</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79642</t>
+          <t>80216</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109745</t>
+          <t>108825</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>216491</t>
+          <t>217197</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>266589</t>
+          <t>269066</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>306145</t>
+          <t>305956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>367938</t>
+          <t>367460</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>102488</t>
+          <t>103408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>132591</t>
+          <t>132017</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>679027</t>
+          <t>676550</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>729125</t>
+          <t>728419</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>789911</t>
+          <t>790389</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>851704</t>
+          <t>851893</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>684726</t>
+          <t>681247</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>776969</t>
+          <t>774736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>811432</t>
+          <t>812111</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>910316</t>
+          <t>910107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1522879</t>
+          <t>1518224</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1655008</t>
+          <t>1651016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1672923</t>
+          <t>1675156</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1765166</t>
+          <t>1768645</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1828617</t>
+          <t>1828826</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1927501</t>
+          <t>1926822</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3533817</t>
+          <t>3537809</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3665946</t>
+          <t>3670601</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,74%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124383</t>
+          <t>124109</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165526</t>
+          <t>165763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117289</t>
+          <t>116059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>151950</t>
+          <t>151548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252853</t>
+          <t>250397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>306637</t>
+          <t>307736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229818</t>
+          <t>229581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270961</t>
+          <t>271235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142004</t>
+          <t>142406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176665</t>
+          <t>177895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>382662</t>
+          <t>381563</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436446</t>
+          <t>438902</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121475</t>
+          <t>122448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161963</t>
+          <t>163595</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>124641</t>
+          <t>127679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160404</t>
+          <t>163342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255260</t>
+          <t>257771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>313819</t>
+          <t>312875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>221761</t>
+          <t>220129</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262249</t>
+          <t>261276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153097</t>
+          <t>150159</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>188860</t>
+          <t>185822</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>383406</t>
+          <t>384350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>441965</t>
+          <t>439454</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,03%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121870</t>
+          <t>122413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162525</t>
+          <t>167092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63962</t>
+          <t>63885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93028</t>
+          <t>93515</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197369</t>
+          <t>195160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>247794</t>
+          <t>244983</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>372963</t>
+          <t>368396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>413618</t>
+          <t>413075</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147608</t>
+          <t>147121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176674</t>
+          <t>176751</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>528330</t>
+          <t>531141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578755</t>
+          <t>580964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205319</t>
+          <t>205438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>263389</t>
+          <t>261214</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>222946</t>
+          <t>221992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275125</t>
+          <t>272513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>445556</t>
+          <t>440447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>518960</t>
+          <t>515599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>709340</t>
+          <t>711515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>767410</t>
+          <t>767291</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>422805</t>
+          <t>425417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474984</t>
+          <t>475938</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1151698</t>
+          <t>1155059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1225102</t>
+          <t>1230211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69920</t>
+          <t>67646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101817</t>
+          <t>101390</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>150316</t>
+          <t>149656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197604</t>
+          <t>199506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231837</t>
+          <t>230687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>288047</t>
+          <t>292463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>301495</t>
+          <t>301922</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333392</t>
+          <t>335666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472219</t>
+          <t>470317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>519507</t>
+          <t>520167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>785088</t>
+          <t>780672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>841298</t>
+          <t>842448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,5%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97192</t>
+          <t>98147</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126605</t>
+          <t>125659</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>269655</t>
+          <t>267814</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326023</t>
+          <t>327595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>380695</t>
+          <t>378388</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>446472</t>
+          <t>441886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94598</t>
+          <t>95544</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124011</t>
+          <t>123056</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>599362</t>
+          <t>597790</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>655730</t>
+          <t>657571</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>700116</t>
+          <t>704702</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>765893</t>
+          <t>768200</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>802590</t>
+          <t>804340</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>906116</t>
+          <t>904305</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1025778</t>
+          <t>1023094</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1138141</t>
+          <t>1129271</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1857845</t>
+          <t>1857710</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2006713</t>
+          <t>2009031</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2005684</t>
+          <t>2007495</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2109210</t>
+          <t>2107460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2003089</t>
+          <t>2011959</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2115452</t>
+          <t>2118136</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4046317</t>
+          <t>4043999</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4195185</t>
+          <t>4195320</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>176436</t>
+          <t>178029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>218797</t>
+          <t>218054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149439</t>
+          <t>150599</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>184917</t>
+          <t>185470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>337592</t>
+          <t>338948</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>392556</t>
+          <t>394832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168817</t>
+          <t>169560</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>211178</t>
+          <t>209585</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130899</t>
+          <t>130346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>166377</t>
+          <t>165217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>310874</t>
+          <t>308598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>365838</t>
+          <t>364482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>130210</t>
+          <t>127928</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165226</t>
+          <t>165120</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161432</t>
+          <t>162598</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>198920</t>
+          <t>199218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302049</t>
+          <t>301679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>355949</t>
+          <t>354641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,54%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151432</t>
+          <t>151538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186448</t>
+          <t>188730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134655</t>
+          <t>134357</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172143</t>
+          <t>170977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>294283</t>
+          <t>295591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>348183</t>
+          <t>348553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,6%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133406</t>
+          <t>134590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174397</t>
+          <t>173354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57384</t>
+          <t>58811</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176770</t>
+          <t>177895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>223566</t>
+          <t>222308</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>230814</t>
+          <t>231857</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271805</t>
+          <t>270621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82037</t>
+          <t>80610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103372</t>
+          <t>104200</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>321067</t>
+          <t>322325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>367863</t>
+          <t>366738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>294111</t>
+          <t>295728</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>353012</t>
+          <t>351951</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>244318</t>
+          <t>242399</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>297020</t>
+          <t>297469</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>552036</t>
+          <t>555609</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>631362</t>
+          <t>630947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>526493</t>
+          <t>527554</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>585394</t>
+          <t>583777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>387011</t>
+          <t>386562</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>439713</t>
+          <t>441632</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>932174</t>
+          <t>932589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1011500</t>
+          <t>1007927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,46%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>109342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149166</t>
+          <t>148821</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>188516</t>
+          <t>187572</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>233672</t>
+          <t>234012</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>308879</t>
+          <t>308462</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>368662</t>
+          <t>369805</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>276003</t>
+          <t>276348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>314738</t>
+          <t>315827</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>323809</t>
+          <t>323469</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>368965</t>
+          <t>369909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>613988</t>
+          <t>612845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>673771</t>
+          <t>674188</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,61%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>117574</t>
+          <t>118772</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>148151</t>
+          <t>148379</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>337935</t>
+          <t>338088</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>394612</t>
+          <t>395696</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>466259</t>
+          <t>466885</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>531562</t>
+          <t>534082</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93397</t>
+          <t>93169</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123974</t>
+          <t>122776</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>430677</t>
+          <t>429593</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>487354</t>
+          <t>487201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>535275</t>
+          <t>532755</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>600578</t>
+          <t>599952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1023991</t>
+          <t>1030263</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1131710</t>
+          <t>1133767</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1193032</t>
+          <t>1188231</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1296669</t>
+          <t>1293103</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2247329</t>
+          <t>2255306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2396034</t>
+          <t>2400734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1523995</t>
+          <t>1521938</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1631714</t>
+          <t>1625442</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1558944</t>
+          <t>1562510</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1662581</t>
+          <t>1667382</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3115284</t>
+          <t>3110584</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3263989</t>
+          <t>3256012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,08%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>338416</t>
+          <t>369217</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>317417</t>
+          <t>345504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>359018</t>
+          <t>390653</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>294477</t>
+          <t>323518</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>276292</t>
+          <t>306427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>310157</t>
+          <t>341165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>692735</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>604120</t>
+          <t>663807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>658877</t>
+          <t>721375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,48%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>160770</t>
+          <t>172998</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140168</t>
+          <t>151562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181769</t>
+          <t>196711</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>157809</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130768</t>
+          <t>140162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164633</t>
+          <t>174900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>307218</t>
+          <t>330806</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>281234</t>
+          <t>302166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>335991</t>
+          <t>359734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>499186</t>
+          <t>542215</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>499186</t>
+          <t>542215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>499186</t>
+          <t>542215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>940111</t>
+          <t>1023541</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>940111</t>
+          <t>1023541</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>940111</t>
+          <t>1023541</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>294433</t>
+          <t>312115</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>275568</t>
+          <t>289462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>316233</t>
+          <t>333518</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>255817</t>
+          <t>285775</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240091</t>
+          <t>269447</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>272882</t>
+          <t>304068</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>550250</t>
+          <t>597891</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>522701</t>
+          <t>568581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>573130</t>
+          <t>625017</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,66%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>153985</t>
+          <t>167217</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132185</t>
+          <t>145814</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172850</t>
+          <t>189870</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>121789</t>
+          <t>132145</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>104724</t>
+          <t>113852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>137515</t>
+          <t>148473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>275773</t>
+          <t>299362</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>252893</t>
+          <t>272236</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>303322</t>
+          <t>328672</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>234748</t>
+          <t>258000</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93586</t>
+          <t>235819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>382921</t>
+          <t>280591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>91804</t>
+          <t>103693</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>92737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102132</t>
+          <t>115071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>326551</t>
+          <t>361694</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137756</t>
+          <t>336403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>474993</t>
+          <t>386162</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>59,53%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>425981</t>
+          <t>205865</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277808</t>
+          <t>183274</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>567143</t>
+          <t>228046</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73164</t>
+          <t>81140</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62836</t>
+          <t>69762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83653</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>499146</t>
+          <t>287004</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>350704</t>
+          <t>262536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>687941</t>
+          <t>312295</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>48,14%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>516766</t>
+          <t>573043</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>481880</t>
+          <t>539061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>548228</t>
+          <t>609544</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>457130</t>
+          <t>505725</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>241065</t>
+          <t>480882</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>592223</t>
+          <t>530494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>973897</t>
+          <t>1078768</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>719083</t>
+          <t>1028530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1103506</t>
+          <t>1122125</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>481385</t>
+          <t>522656</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>449923</t>
+          <t>486155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>516271</t>
+          <t>556638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>501739</t>
+          <t>331065</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366646</t>
+          <t>306296</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>717804</t>
+          <t>355908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>983123</t>
+          <t>853721</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>853514</t>
+          <t>810364</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1237937</t>
+          <t>903959</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>46,78%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>203960</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>183013</t>
+          <t>202785</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227579</t>
+          <t>251092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>422113</t>
+          <t>397964</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>367758</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>509445</t>
+          <t>421890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>626073</t>
+          <t>622386</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>568037</t>
+          <t>583730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>729429</t>
+          <t>655273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>234892</t>
+          <t>285426</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>258756</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255839</t>
+          <t>307063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>391868</t>
+          <t>395541</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>304536</t>
+          <t>371615</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446223</t>
+          <t>420360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>626760</t>
+          <t>680967</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>523404</t>
+          <t>648080</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>684796</t>
+          <t>719623</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,21%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>153437</t>
+          <t>147805</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126462</t>
+          <t>123122</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177681</t>
+          <t>170919</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>429637</t>
+          <t>473891</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>401959</t>
+          <t>445436</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>455152</t>
+          <t>502369</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>583074</t>
+          <t>621696</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>544289</t>
+          <t>585597</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>619301</t>
+          <t>659437</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>79775</t>
+          <t>77982</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55531</t>
+          <t>54868</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>106750</t>
+          <t>102665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>314273</t>
+          <t>344851</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>288758</t>
+          <t>316373</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>341951</t>
+          <t>373306</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>394048</t>
+          <t>422833</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>357821</t>
+          <t>385092</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>432833</t>
+          <t>458932</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1741760</t>
+          <t>1884604</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1333874</t>
+          <t>1822358</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1898138</t>
+          <t>1951494</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1950979</t>
+          <t>2090567</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1538777</t>
+          <t>2038719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2107687</t>
+          <t>2143028</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3692739</t>
+          <t>3975170</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3193359</t>
+          <t>3886140</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3968116</t>
+          <t>4052280</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1536788</t>
+          <t>1432143</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1380410</t>
+          <t>1365253</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1944674</t>
+          <t>1494389</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1549280</t>
+          <t>1442551</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1392572</t>
+          <t>1390090</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1961482</t>
+          <t>1494399</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3086068</t>
+          <t>2874694</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2810691</t>
+          <t>2797584</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3585448</t>
+          <t>2963724</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3278548</t>
+          <t>3316747</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3278548</t>
+          <t>3316747</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3278548</t>
+          <t>3316747</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6778807</t>
+          <t>6849864</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6778807</t>
+          <t>6849864</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6778807</t>
+          <t>6849864</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
